--- a/output/yearly_population_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_100_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4128</v>
+        <v>4693</v>
       </c>
       <c r="C2" t="n">
-        <v>7812</v>
+        <v>5991</v>
       </c>
       <c r="D2" t="n">
-        <v>20534</v>
+        <v>22551</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3045</v>
+        <v>3087</v>
       </c>
       <c r="C3" t="n">
-        <v>6625</v>
+        <v>4515</v>
       </c>
       <c r="D3" t="n">
-        <v>16346</v>
+        <v>17982</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2620</v>
+        <v>2495</v>
       </c>
       <c r="C4" t="n">
-        <v>5520</v>
+        <v>5453</v>
       </c>
       <c r="D4" t="n">
-        <v>8433</v>
+        <v>10310</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1667</v>
+        <v>1545</v>
       </c>
       <c r="C5" t="n">
-        <v>4965</v>
+        <v>5125</v>
       </c>
       <c r="D5" t="n">
-        <v>3211</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>935</v>
+        <v>826</v>
       </c>
       <c r="C6" t="n">
-        <v>3579</v>
+        <v>3431</v>
       </c>
       <c r="D6" t="n">
-        <v>1293</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>389</v>
       </c>
       <c r="C7" t="n">
-        <v>2213</v>
+        <v>1784</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>1029</v>
+        <v>794</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>420</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>163</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5063</v>
+        <v>6904</v>
       </c>
       <c r="C2" t="n">
-        <v>9433</v>
+        <v>7337</v>
       </c>
       <c r="D2" t="n">
-        <v>18854</v>
+        <v>34198</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2877</v>
+        <v>3079</v>
       </c>
       <c r="C3" t="n">
-        <v>6307</v>
+        <v>4602</v>
       </c>
       <c r="D3" t="n">
-        <v>15809</v>
+        <v>17567</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2399</v>
+        <v>2348</v>
       </c>
       <c r="C4" t="n">
-        <v>5861</v>
+        <v>4854</v>
       </c>
       <c r="D4" t="n">
-        <v>9311</v>
+        <v>11076</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1825</v>
+        <v>1714</v>
       </c>
       <c r="C5" t="n">
-        <v>5112</v>
+        <v>5117</v>
       </c>
       <c r="D5" t="n">
-        <v>3915</v>
+        <v>4796</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1138</v>
+        <v>1023</v>
       </c>
       <c r="C6" t="n">
-        <v>4109</v>
+        <v>4146</v>
       </c>
       <c r="D6" t="n">
-        <v>1539</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>573</v>
+        <v>516</v>
       </c>
       <c r="C7" t="n">
-        <v>2801</v>
+        <v>2475</v>
       </c>
       <c r="D7" t="n">
-        <v>759</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C8" t="n">
-        <v>1505</v>
+        <v>1210</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>664</v>
+        <v>514</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>255</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6931</v>
+        <v>7559</v>
       </c>
       <c r="C2" t="n">
-        <v>8834</v>
+        <v>5076</v>
       </c>
       <c r="D2" t="n">
-        <v>35060</v>
+        <v>42402</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3042</v>
+        <v>3696</v>
       </c>
       <c r="C3" t="n">
-        <v>6711</v>
+        <v>5056</v>
       </c>
       <c r="D3" t="n">
-        <v>15162</v>
+        <v>18438</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2235</v>
+        <v>2250</v>
       </c>
       <c r="C4" t="n">
-        <v>5871</v>
+        <v>4599</v>
       </c>
       <c r="D4" t="n">
-        <v>9963</v>
+        <v>11567</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1828</v>
+        <v>1765</v>
       </c>
       <c r="C5" t="n">
-        <v>5314</v>
+        <v>4852</v>
       </c>
       <c r="D5" t="n">
-        <v>4483</v>
+        <v>5554</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1277</v>
+        <v>1171</v>
       </c>
       <c r="C6" t="n">
-        <v>4428</v>
+        <v>4501</v>
       </c>
       <c r="D6" t="n">
-        <v>1823</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>707</v>
+        <v>636</v>
       </c>
       <c r="C7" t="n">
-        <v>3285</v>
+        <v>3104</v>
       </c>
       <c r="D7" t="n">
-        <v>858</v>
+        <v>919</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="C8" t="n">
-        <v>1999</v>
+        <v>1681</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C9" t="n">
-        <v>962</v>
+        <v>772</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>420</v>
+        <v>343</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1576,7 +1576,7 @@
         <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6251</v>
+        <v>6904</v>
       </c>
       <c r="C2" t="n">
-        <v>6148</v>
+        <v>3492</v>
       </c>
       <c r="D2" t="n">
-        <v>28775</v>
+        <v>34806</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3796</v>
+        <v>4215</v>
       </c>
       <c r="C3" t="n">
-        <v>9841</v>
+        <v>7364</v>
       </c>
       <c r="D3" t="n">
-        <v>16888</v>
+        <v>20368</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1689</v>
+        <v>1630</v>
       </c>
       <c r="C4" t="n">
-        <v>8257</v>
+        <v>7130</v>
       </c>
       <c r="D4" t="n">
-        <v>9602</v>
+        <v>11389</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1179</v>
+        <v>1082</v>
       </c>
       <c r="C5" t="n">
-        <v>4339</v>
+        <v>4410</v>
       </c>
       <c r="D5" t="n">
-        <v>2991</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>653</v>
+        <v>587</v>
       </c>
       <c r="C6" t="n">
-        <v>3219</v>
+        <v>3041</v>
       </c>
       <c r="D6" t="n">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="C7" t="n">
-        <v>1959</v>
+        <v>1647</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>942</v>
+        <v>756</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>336</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1873,7 +1873,7 @@
         <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3756</v>
+        <v>3982</v>
       </c>
       <c r="C2" t="n">
-        <v>3276</v>
+        <v>1952</v>
       </c>
       <c r="D2" t="n">
-        <v>19532</v>
+        <v>25139</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4117</v>
+        <v>4615</v>
       </c>
       <c r="C3" t="n">
-        <v>7466</v>
+        <v>5171</v>
       </c>
       <c r="D3" t="n">
-        <v>17694</v>
+        <v>21353</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2160</v>
+        <v>2240</v>
       </c>
       <c r="C4" t="n">
-        <v>9037</v>
+        <v>7292</v>
       </c>
       <c r="D4" t="n">
-        <v>10451</v>
+        <v>12445</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1304</v>
+        <v>1203</v>
       </c>
       <c r="C5" t="n">
-        <v>6036</v>
+        <v>5626</v>
       </c>
       <c r="D5" t="n">
-        <v>3811</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>766</v>
+        <v>701</v>
       </c>
       <c r="C6" t="n">
-        <v>3792</v>
+        <v>3657</v>
       </c>
       <c r="D6" t="n">
-        <v>1040</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
-        <v>2432</v>
+        <v>2160</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>1248</v>
+        <v>1003</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>445</v>
+        <v>380</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3979</v>
+        <v>3993</v>
       </c>
       <c r="C2" t="n">
-        <v>12327</v>
+        <v>6620</v>
       </c>
       <c r="D2" t="n">
-        <v>17101</v>
+        <v>23027</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3366</v>
+        <v>3657</v>
       </c>
       <c r="C3" t="n">
-        <v>4920</v>
+        <v>3278</v>
       </c>
       <c r="D3" t="n">
-        <v>16754</v>
+        <v>20432</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2544</v>
+        <v>2795</v>
       </c>
       <c r="C4" t="n">
-        <v>8094</v>
+        <v>6122</v>
       </c>
       <c r="D4" t="n">
-        <v>11315</v>
+        <v>13520</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1482</v>
+        <v>1447</v>
       </c>
       <c r="C5" t="n">
-        <v>7351</v>
+        <v>6276</v>
       </c>
       <c r="D5" t="n">
-        <v>4715</v>
+        <v>5625</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>903</v>
+        <v>829</v>
       </c>
       <c r="C6" t="n">
-        <v>4725</v>
+        <v>4527</v>
       </c>
       <c r="D6" t="n">
-        <v>1425</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>411</v>
+        <v>374</v>
       </c>
       <c r="C7" t="n">
-        <v>3027</v>
+        <v>2789</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1723</v>
+        <v>1477</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>740</v>
+        <v>619</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2367</v>
+        <v>2379</v>
       </c>
       <c r="C2" t="n">
-        <v>5851</v>
+        <v>3085</v>
       </c>
       <c r="D2" t="n">
-        <v>11953</v>
+        <v>16098</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3386</v>
+        <v>3605</v>
       </c>
       <c r="C3" t="n">
-        <v>7207</v>
+        <v>4301</v>
       </c>
       <c r="D3" t="n">
-        <v>16414</v>
+        <v>20244</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2827</v>
+        <v>3067</v>
       </c>
       <c r="C4" t="n">
-        <v>7697</v>
+        <v>5712</v>
       </c>
       <c r="D4" t="n">
-        <v>12029</v>
+        <v>14409</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1557</v>
+        <v>1485</v>
       </c>
       <c r="C5" t="n">
-        <v>8730</v>
+        <v>7224</v>
       </c>
       <c r="D5" t="n">
-        <v>4960</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>738</v>
+        <v>682</v>
       </c>
       <c r="C6" t="n">
-        <v>5567</v>
+        <v>5373</v>
       </c>
       <c r="D6" t="n">
-        <v>1386</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>3169</v>
+        <v>2830</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>1231</v>
+        <v>1055</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2399</v>
+        <v>2609</v>
       </c>
       <c r="C2" t="n">
-        <v>7577</v>
+        <v>7273</v>
       </c>
       <c r="D2" t="n">
-        <v>11552</v>
+        <v>15699</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2546</v>
+        <v>2653</v>
       </c>
       <c r="C3" t="n">
-        <v>5891</v>
+        <v>3339</v>
       </c>
       <c r="D3" t="n">
-        <v>14861</v>
+        <v>18514</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2661</v>
+        <v>2896</v>
       </c>
       <c r="C4" t="n">
-        <v>7385</v>
+        <v>4984</v>
       </c>
       <c r="D4" t="n">
-        <v>12336</v>
+        <v>14867</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1835</v>
+        <v>1861</v>
       </c>
       <c r="C5" t="n">
-        <v>8102</v>
+        <v>6475</v>
       </c>
       <c r="D5" t="n">
-        <v>5827</v>
+        <v>6954</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>950</v>
+        <v>885</v>
       </c>
       <c r="C6" t="n">
-        <v>6931</v>
+        <v>6141</v>
       </c>
       <c r="D6" t="n">
-        <v>1861</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C7" t="n">
-        <v>4115</v>
+        <v>3881</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1938</v>
+        <v>1701</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>599</v>
+        <v>521</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
         <v>100</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1766</v>
+        <v>1743</v>
       </c>
       <c r="C2" t="n">
-        <v>5366</v>
+        <v>4333</v>
       </c>
       <c r="D2" t="n">
-        <v>8806</v>
+        <v>13359</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2192</v>
+        <v>2312</v>
       </c>
       <c r="C3" t="n">
-        <v>5943</v>
+        <v>4419</v>
       </c>
       <c r="D3" t="n">
-        <v>13705</v>
+        <v>17169</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2420</v>
+        <v>2602</v>
       </c>
       <c r="C4" t="n">
-        <v>6856</v>
+        <v>4360</v>
       </c>
       <c r="D4" t="n">
-        <v>12394</v>
+        <v>15190</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1968</v>
+        <v>2038</v>
       </c>
       <c r="C5" t="n">
-        <v>7919</v>
+        <v>5997</v>
       </c>
       <c r="D5" t="n">
-        <v>6449</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1103</v>
+        <v>1060</v>
       </c>
       <c r="C6" t="n">
-        <v>7573</v>
+        <v>6562</v>
       </c>
       <c r="D6" t="n">
-        <v>2180</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C7" t="n">
-        <v>5057</v>
+        <v>4639</v>
       </c>
       <c r="D7" t="n">
-        <v>751</v>
+        <v>817</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>2463</v>
+        <v>2234</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>676</v>
+        <v>596</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2516</v>
+        <v>2145</v>
       </c>
       <c r="C2" t="n">
-        <v>10238</v>
+        <v>6114</v>
       </c>
       <c r="D2" t="n">
-        <v>13231</v>
+        <v>17005</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1722</v>
+        <v>1776</v>
       </c>
       <c r="C3" t="n">
-        <v>5097</v>
+        <v>3900</v>
       </c>
       <c r="D3" t="n">
-        <v>12371</v>
+        <v>15612</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2055</v>
+        <v>2194</v>
       </c>
       <c r="C4" t="n">
-        <v>6336</v>
+        <v>4294</v>
       </c>
       <c r="D4" t="n">
-        <v>12074</v>
+        <v>15013</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1932</v>
+        <v>2030</v>
       </c>
       <c r="C5" t="n">
-        <v>7335</v>
+        <v>5212</v>
       </c>
       <c r="D5" t="n">
-        <v>7051</v>
+        <v>8425</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C6" t="n">
-        <v>7640</v>
+        <v>6289</v>
       </c>
       <c r="D6" t="n">
-        <v>2684</v>
+        <v>3179</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C7" t="n">
-        <v>6016</v>
+        <v>5353</v>
       </c>
       <c r="D7" t="n">
-        <v>911</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>3326</v>
+        <v>3103</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1242</v>
+        <v>1131</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3711,7 +3711,7 @@
         <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>38</v>
+      </c>
+      <c r="D14" t="n">
         <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5390</v>
+        <v>4654</v>
       </c>
       <c r="C2" t="n">
-        <v>9717</v>
+        <v>4827</v>
       </c>
       <c r="D2" t="n">
-        <v>13971</v>
+        <v>18443</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1838</v>
+        <v>1536</v>
       </c>
       <c r="C2" t="n">
-        <v>5978</v>
+        <v>3521</v>
       </c>
       <c r="D2" t="n">
-        <v>9843</v>
+        <v>12516</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2331</v>
+        <v>2412</v>
       </c>
       <c r="C3" t="n">
-        <v>6664</v>
+        <v>4701</v>
       </c>
       <c r="D3" t="n">
-        <v>13428</v>
+        <v>17084</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2817</v>
+        <v>2978</v>
       </c>
       <c r="C4" t="n">
-        <v>8917</v>
+        <v>6135</v>
       </c>
       <c r="D4" t="n">
-        <v>12471</v>
+        <v>15425</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1226</v>
+        <v>1246</v>
       </c>
       <c r="C5" t="n">
-        <v>10786</v>
+        <v>8332</v>
       </c>
       <c r="D5" t="n">
-        <v>6418</v>
+        <v>7623</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C6" t="n">
-        <v>7243</v>
+        <v>6478</v>
       </c>
       <c r="D6" t="n">
-        <v>2065</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>3259</v>
+        <v>3040</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1217</v>
+        <v>1108</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4319,7 +4319,7 @@
         <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
         <v>92</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>37</v>
+      </c>
+      <c r="D13" t="n">
         <v>36</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6028</v>
+        <v>5576</v>
       </c>
       <c r="C2" t="n">
-        <v>8911</v>
+        <v>9093</v>
       </c>
       <c r="D2" t="n">
-        <v>26091</v>
+        <v>27108</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2290</v>
+        <v>1978</v>
       </c>
       <c r="C3" t="n">
-        <v>4897</v>
+        <v>2432</v>
       </c>
       <c r="D3" t="n">
-        <v>2986</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5022</v>
+        <v>4351</v>
       </c>
       <c r="C2" t="n">
-        <v>4014</v>
+        <v>5724</v>
       </c>
       <c r="D2" t="n">
-        <v>23851</v>
+        <v>33294</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3415</v>
+        <v>3100</v>
       </c>
       <c r="C3" t="n">
-        <v>6182</v>
+        <v>5347</v>
       </c>
       <c r="D3" t="n">
-        <v>6647</v>
+        <v>7388</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1029</v>
+        <v>893</v>
       </c>
       <c r="C4" t="n">
-        <v>2913</v>
+        <v>1470</v>
       </c>
       <c r="D4" t="n">
-        <v>1783</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4872</v>
+        <v>4001</v>
       </c>
       <c r="C2" t="n">
-        <v>11393</v>
+        <v>7813</v>
       </c>
       <c r="D2" t="n">
-        <v>28223</v>
+        <v>41366</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3481</v>
+        <v>3052</v>
       </c>
       <c r="C3" t="n">
-        <v>4355</v>
+        <v>4811</v>
       </c>
       <c r="D3" t="n">
-        <v>8921</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1861</v>
+        <v>1697</v>
       </c>
       <c r="C4" t="n">
-        <v>4672</v>
+        <v>3584</v>
       </c>
       <c r="D4" t="n">
-        <v>2662</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>475</v>
+        <v>419</v>
       </c>
       <c r="C5" t="n">
-        <v>1663</v>
+        <v>901</v>
       </c>
       <c r="D5" t="n">
-        <v>1256</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5319,7 +5319,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5210</v>
+        <v>4822</v>
       </c>
       <c r="C2" t="n">
-        <v>6703</v>
+        <v>11706</v>
       </c>
       <c r="D2" t="n">
-        <v>24556</v>
+        <v>38816</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3394</v>
+        <v>2876</v>
       </c>
       <c r="C3" t="n">
-        <v>6894</v>
+        <v>5516</v>
       </c>
       <c r="D3" t="n">
-        <v>11226</v>
+        <v>14842</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2252</v>
+        <v>1991</v>
       </c>
       <c r="C4" t="n">
-        <v>4407</v>
+        <v>4122</v>
       </c>
       <c r="D4" t="n">
-        <v>3722</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="C5" t="n">
-        <v>3143</v>
+        <v>2273</v>
       </c>
       <c r="D5" t="n">
-        <v>1448</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>980</v>
+        <v>599</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
         <v>666</v>
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,7 +5557,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
         <v>233</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6219</v>
+        <v>6310</v>
       </c>
       <c r="C2" t="n">
-        <v>8942</v>
+        <v>8154</v>
       </c>
       <c r="D2" t="n">
-        <v>35503</v>
+        <v>31581</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3091</v>
+        <v>2756</v>
       </c>
       <c r="C3" t="n">
-        <v>5573</v>
+        <v>7064</v>
       </c>
       <c r="D3" t="n">
-        <v>11724</v>
+        <v>16409</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1729</v>
+        <v>1492</v>
       </c>
       <c r="C4" t="n">
-        <v>4707</v>
+        <v>3989</v>
       </c>
       <c r="D4" t="n">
-        <v>4343</v>
+        <v>5322</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>828</v>
+        <v>738</v>
       </c>
       <c r="C5" t="n">
-        <v>2737</v>
+        <v>2330</v>
       </c>
       <c r="D5" t="n">
-        <v>1444</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>1379</v>
+        <v>960</v>
       </c>
       <c r="D6" t="n">
-        <v>790</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>414</v>
+        <v>298</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
         <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
         <v>272</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5008</v>
+        <v>4948</v>
       </c>
       <c r="C2" t="n">
-        <v>6278</v>
+        <v>5255</v>
       </c>
       <c r="D2" t="n">
-        <v>28504</v>
+        <v>29135</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3877</v>
+        <v>3752</v>
       </c>
       <c r="C3" t="n">
-        <v>6468</v>
+        <v>6621</v>
       </c>
       <c r="D3" t="n">
-        <v>14855</v>
+        <v>17750</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2079</v>
+        <v>1856</v>
       </c>
       <c r="C4" t="n">
-        <v>5124</v>
+        <v>5736</v>
       </c>
       <c r="D4" t="n">
-        <v>5698</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1134</v>
+        <v>990</v>
       </c>
       <c r="C5" t="n">
-        <v>3814</v>
+        <v>3237</v>
       </c>
       <c r="D5" t="n">
-        <v>1942</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>504</v>
+        <v>456</v>
       </c>
       <c r="C6" t="n">
-        <v>2118</v>
+        <v>1711</v>
       </c>
       <c r="D6" t="n">
-        <v>904</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>943</v>
+        <v>658</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>321</v>
+        <v>262</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>80</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3718</v>
+        <v>3942</v>
       </c>
       <c r="C2" t="n">
-        <v>9739</v>
+        <v>5192</v>
       </c>
       <c r="D2" t="n">
-        <v>26687</v>
+        <v>25222</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3640</v>
+        <v>3562</v>
       </c>
       <c r="C3" t="n">
-        <v>5532</v>
+        <v>5129</v>
       </c>
       <c r="D3" t="n">
-        <v>15883</v>
+        <v>18230</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2542</v>
+        <v>2388</v>
       </c>
       <c r="C4" t="n">
-        <v>5752</v>
+        <v>6045</v>
       </c>
       <c r="D4" t="n">
-        <v>7140</v>
+        <v>8987</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1391</v>
+        <v>1230</v>
       </c>
       <c r="C5" t="n">
-        <v>4389</v>
+        <v>4513</v>
       </c>
       <c r="D5" t="n">
-        <v>2568</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>736</v>
+        <v>651</v>
       </c>
       <c r="C6" t="n">
-        <v>2973</v>
+        <v>2482</v>
       </c>
       <c r="D6" t="n">
-        <v>1062</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C7" t="n">
-        <v>1541</v>
+        <v>1187</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>622</v>
+        <v>459</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>

--- a/output/yearly_population_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_100_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4693</v>
+        <v>6977</v>
       </c>
       <c r="C2" t="n">
-        <v>5991</v>
+        <v>5881</v>
       </c>
       <c r="D2" t="n">
-        <v>22551</v>
+        <v>26040</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3087</v>
+        <v>3711</v>
       </c>
       <c r="C3" t="n">
-        <v>4515</v>
+        <v>3987</v>
       </c>
       <c r="D3" t="n">
-        <v>17982</v>
+        <v>15872</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2495</v>
+        <v>2964</v>
       </c>
       <c r="C4" t="n">
-        <v>5453</v>
+        <v>4935</v>
       </c>
       <c r="D4" t="n">
-        <v>10310</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1545</v>
+        <v>2016</v>
       </c>
       <c r="C5" t="n">
-        <v>5125</v>
+        <v>3281</v>
       </c>
       <c r="D5" t="n">
-        <v>3937</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>1256</v>
       </c>
       <c r="C6" t="n">
-        <v>3431</v>
+        <v>1941</v>
       </c>
       <c r="D6" t="n">
-        <v>1442</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>389</v>
+        <v>629</v>
       </c>
       <c r="C7" t="n">
-        <v>1784</v>
+        <v>1179</v>
       </c>
       <c r="D7" t="n">
-        <v>691</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>246</v>
       </c>
       <c r="C8" t="n">
-        <v>794</v>
+        <v>585</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C9" t="n">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6904</v>
+        <v>7964</v>
       </c>
       <c r="C2" t="n">
-        <v>7337</v>
+        <v>12406</v>
       </c>
       <c r="D2" t="n">
-        <v>34198</v>
+        <v>30265</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3079</v>
+        <v>4202</v>
       </c>
       <c r="C3" t="n">
-        <v>4602</v>
+        <v>4283</v>
       </c>
       <c r="D3" t="n">
-        <v>17567</v>
+        <v>16244</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2348</v>
+        <v>2824</v>
       </c>
       <c r="C4" t="n">
-        <v>4854</v>
+        <v>4359</v>
       </c>
       <c r="D4" t="n">
-        <v>11076</v>
+        <v>8336</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1714</v>
+        <v>2159</v>
       </c>
       <c r="C5" t="n">
-        <v>5117</v>
+        <v>3975</v>
       </c>
       <c r="D5" t="n">
-        <v>4796</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1023</v>
+        <v>1471</v>
       </c>
       <c r="C6" t="n">
-        <v>4146</v>
+        <v>2551</v>
       </c>
       <c r="D6" t="n">
-        <v>1768</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>516</v>
+        <v>812</v>
       </c>
       <c r="C7" t="n">
-        <v>2475</v>
+        <v>1517</v>
       </c>
       <c r="D7" t="n">
-        <v>794</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>217</v>
+        <v>366</v>
       </c>
       <c r="C8" t="n">
-        <v>1210</v>
+        <v>852</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>514</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7559</v>
+        <v>9970</v>
       </c>
       <c r="C2" t="n">
-        <v>5076</v>
+        <v>10117</v>
       </c>
       <c r="D2" t="n">
-        <v>42402</v>
+        <v>38740</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3696</v>
+        <v>4696</v>
       </c>
       <c r="C3" t="n">
-        <v>5056</v>
+        <v>6901</v>
       </c>
       <c r="D3" t="n">
-        <v>18438</v>
+        <v>16973</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2250</v>
+        <v>2923</v>
       </c>
       <c r="C4" t="n">
-        <v>4599</v>
+        <v>4233</v>
       </c>
       <c r="D4" t="n">
-        <v>11567</v>
+        <v>9217</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1765</v>
+        <v>2171</v>
       </c>
       <c r="C5" t="n">
-        <v>4852</v>
+        <v>4023</v>
       </c>
       <c r="D5" t="n">
-        <v>5554</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1171</v>
+        <v>1608</v>
       </c>
       <c r="C6" t="n">
-        <v>4501</v>
+        <v>3142</v>
       </c>
       <c r="D6" t="n">
-        <v>2134</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>636</v>
+        <v>977</v>
       </c>
       <c r="C7" t="n">
-        <v>3104</v>
+        <v>1937</v>
       </c>
       <c r="D7" t="n">
-        <v>919</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>290</v>
+        <v>489</v>
       </c>
       <c r="C8" t="n">
-        <v>1681</v>
+        <v>1117</v>
       </c>
       <c r="D8" t="n">
         <v>494</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="C9" t="n">
-        <v>772</v>
+        <v>592</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>343</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6904</v>
+        <v>8949</v>
       </c>
       <c r="C2" t="n">
-        <v>3492</v>
+        <v>6717</v>
       </c>
       <c r="D2" t="n">
-        <v>34806</v>
+        <v>31333</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4215</v>
+        <v>5531</v>
       </c>
       <c r="C3" t="n">
-        <v>7364</v>
+        <v>9626</v>
       </c>
       <c r="D3" t="n">
-        <v>20368</v>
+        <v>18695</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1630</v>
+        <v>2006</v>
       </c>
       <c r="C4" t="n">
-        <v>7130</v>
+        <v>6300</v>
       </c>
       <c r="D4" t="n">
-        <v>11389</v>
+        <v>8830</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1082</v>
+        <v>1485</v>
       </c>
       <c r="C5" t="n">
-        <v>4410</v>
+        <v>3079</v>
       </c>
       <c r="D5" t="n">
-        <v>3584</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>587</v>
+        <v>902</v>
       </c>
       <c r="C6" t="n">
-        <v>3041</v>
+        <v>1898</v>
       </c>
       <c r="D6" t="n">
-        <v>900</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>267</v>
+        <v>451</v>
       </c>
       <c r="C7" t="n">
-        <v>1647</v>
+        <v>1094</v>
       </c>
       <c r="D7" t="n">
         <v>484</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>756</v>
+        <v>580</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3982</v>
+        <v>5341</v>
       </c>
       <c r="C2" t="n">
-        <v>1952</v>
+        <v>2976</v>
       </c>
       <c r="D2" t="n">
-        <v>25139</v>
+        <v>21613</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4615</v>
+        <v>6022</v>
       </c>
       <c r="C3" t="n">
-        <v>5171</v>
+        <v>7468</v>
       </c>
       <c r="D3" t="n">
-        <v>21353</v>
+        <v>19587</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2240</v>
+        <v>2961</v>
       </c>
       <c r="C4" t="n">
-        <v>7292</v>
+        <v>8007</v>
       </c>
       <c r="D4" t="n">
-        <v>12445</v>
+        <v>10246</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1203</v>
+        <v>1610</v>
       </c>
       <c r="C5" t="n">
-        <v>5626</v>
+        <v>4523</v>
       </c>
       <c r="D5" t="n">
-        <v>4552</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>701</v>
+        <v>1080</v>
       </c>
       <c r="C6" t="n">
-        <v>3657</v>
+        <v>2414</v>
       </c>
       <c r="D6" t="n">
-        <v>1147</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>251</v>
+        <v>429</v>
       </c>
       <c r="C7" t="n">
-        <v>2160</v>
+        <v>1418</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="C8" t="n">
-        <v>1003</v>
+        <v>750</v>
       </c>
       <c r="D8" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3993</v>
+        <v>6618</v>
       </c>
       <c r="C2" t="n">
-        <v>6620</v>
+        <v>4447</v>
       </c>
       <c r="D2" t="n">
-        <v>23027</v>
+        <v>18365</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3657</v>
+        <v>4804</v>
       </c>
       <c r="C3" t="n">
-        <v>3278</v>
+        <v>4631</v>
       </c>
       <c r="D3" t="n">
-        <v>20432</v>
+        <v>18531</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2795</v>
+        <v>3719</v>
       </c>
       <c r="C4" t="n">
-        <v>6122</v>
+        <v>7566</v>
       </c>
       <c r="D4" t="n">
-        <v>13520</v>
+        <v>11548</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1447</v>
+        <v>1946</v>
       </c>
       <c r="C5" t="n">
-        <v>6276</v>
+        <v>6178</v>
       </c>
       <c r="D5" t="n">
-        <v>5625</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>829</v>
+        <v>1209</v>
       </c>
       <c r="C6" t="n">
-        <v>4527</v>
+        <v>3361</v>
       </c>
       <c r="D6" t="n">
-        <v>1622</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>374</v>
+        <v>616</v>
       </c>
       <c r="C7" t="n">
-        <v>2789</v>
+        <v>1880</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>218</v>
       </c>
       <c r="C8" t="n">
-        <v>1477</v>
+        <v>1038</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>619</v>
+        <v>519</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2379</v>
+        <v>3882</v>
       </c>
       <c r="C2" t="n">
-        <v>3085</v>
+        <v>2008</v>
       </c>
       <c r="D2" t="n">
-        <v>16098</v>
+        <v>12660</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3605</v>
+        <v>5067</v>
       </c>
       <c r="C3" t="n">
-        <v>4301</v>
+        <v>4410</v>
       </c>
       <c r="D3" t="n">
-        <v>20244</v>
+        <v>18067</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3067</v>
+        <v>4124</v>
       </c>
       <c r="C4" t="n">
-        <v>5712</v>
+        <v>7120</v>
       </c>
       <c r="D4" t="n">
-        <v>14409</v>
+        <v>12421</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>2070</v>
       </c>
       <c r="C5" t="n">
-        <v>7224</v>
+        <v>7390</v>
       </c>
       <c r="D5" t="n">
-        <v>5910</v>
+        <v>4888</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>682</v>
+        <v>1071</v>
       </c>
       <c r="C6" t="n">
-        <v>5373</v>
+        <v>4148</v>
       </c>
       <c r="D6" t="n">
-        <v>1564</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="C7" t="n">
-        <v>2830</v>
+        <v>1952</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1055</v>
+        <v>844</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2609</v>
+        <v>4440</v>
       </c>
       <c r="C2" t="n">
-        <v>7273</v>
+        <v>5196</v>
       </c>
       <c r="D2" t="n">
-        <v>15699</v>
+        <v>13479</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2653</v>
+        <v>3894</v>
       </c>
       <c r="C3" t="n">
-        <v>3339</v>
+        <v>2909</v>
       </c>
       <c r="D3" t="n">
-        <v>18514</v>
+        <v>16117</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2896</v>
+        <v>3940</v>
       </c>
       <c r="C4" t="n">
-        <v>4984</v>
+        <v>5713</v>
       </c>
       <c r="D4" t="n">
-        <v>14867</v>
+        <v>12964</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1861</v>
+        <v>2581</v>
       </c>
       <c r="C5" t="n">
-        <v>6475</v>
+        <v>7182</v>
       </c>
       <c r="D5" t="n">
-        <v>6954</v>
+        <v>5896</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>885</v>
+        <v>1343</v>
       </c>
       <c r="C6" t="n">
-        <v>6141</v>
+        <v>5550</v>
       </c>
       <c r="D6" t="n">
-        <v>2127</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>257</v>
+        <v>421</v>
       </c>
       <c r="C7" t="n">
-        <v>3881</v>
+        <v>2893</v>
       </c>
       <c r="D7" t="n">
-        <v>723</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>1701</v>
+        <v>1272</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>521</v>
+        <v>466</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1743</v>
+        <v>3383</v>
       </c>
       <c r="C2" t="n">
-        <v>4333</v>
+        <v>2942</v>
       </c>
       <c r="D2" t="n">
-        <v>13359</v>
+        <v>9887</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2312</v>
+        <v>3567</v>
       </c>
       <c r="C3" t="n">
-        <v>4419</v>
+        <v>3476</v>
       </c>
       <c r="D3" t="n">
-        <v>17169</v>
+        <v>14923</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2602</v>
+        <v>3579</v>
       </c>
       <c r="C4" t="n">
-        <v>4360</v>
+        <v>4574</v>
       </c>
       <c r="D4" t="n">
-        <v>15190</v>
+        <v>13118</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2038</v>
+        <v>2856</v>
       </c>
       <c r="C5" t="n">
-        <v>5997</v>
+        <v>6758</v>
       </c>
       <c r="D5" t="n">
-        <v>7644</v>
+        <v>6644</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1060</v>
+        <v>1577</v>
       </c>
       <c r="C6" t="n">
-        <v>6562</v>
+        <v>6300</v>
       </c>
       <c r="D6" t="n">
-        <v>2581</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>233</v>
+        <v>408</v>
       </c>
       <c r="C7" t="n">
-        <v>4639</v>
+        <v>3767</v>
       </c>
       <c r="D7" t="n">
-        <v>817</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>2234</v>
+        <v>1667</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2145</v>
+        <v>5726</v>
       </c>
       <c r="C2" t="n">
-        <v>6114</v>
+        <v>5045</v>
       </c>
       <c r="D2" t="n">
-        <v>17005</v>
+        <v>22560</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1776</v>
+        <v>2943</v>
       </c>
       <c r="C3" t="n">
-        <v>3900</v>
+        <v>2884</v>
       </c>
       <c r="D3" t="n">
-        <v>15612</v>
+        <v>13442</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2194</v>
+        <v>3106</v>
       </c>
       <c r="C4" t="n">
-        <v>4294</v>
+        <v>3993</v>
       </c>
       <c r="D4" t="n">
-        <v>15013</v>
+        <v>12853</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2030</v>
+        <v>2861</v>
       </c>
       <c r="C5" t="n">
-        <v>5212</v>
+        <v>5694</v>
       </c>
       <c r="D5" t="n">
-        <v>8425</v>
+        <v>7374</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1288</v>
+        <v>1879</v>
       </c>
       <c r="C6" t="n">
-        <v>6289</v>
+        <v>6490</v>
       </c>
       <c r="D6" t="n">
-        <v>3179</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>435</v>
+        <v>701</v>
       </c>
       <c r="C7" t="n">
-        <v>5353</v>
+        <v>4733</v>
       </c>
       <c r="D7" t="n">
-        <v>1016</v>
+        <v>956</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>3103</v>
+        <v>2444</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>1131</v>
+        <v>929</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4654</v>
+        <v>8636</v>
       </c>
       <c r="C2" t="n">
-        <v>4827</v>
+        <v>3999</v>
       </c>
       <c r="D2" t="n">
-        <v>18443</v>
+        <v>12932</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1536</v>
+        <v>4052</v>
       </c>
       <c r="C2" t="n">
-        <v>3521</v>
+        <v>2825</v>
       </c>
       <c r="D2" t="n">
-        <v>12516</v>
+        <v>16604</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2412</v>
+        <v>4009</v>
       </c>
       <c r="C3" t="n">
-        <v>4701</v>
+        <v>3647</v>
       </c>
       <c r="D3" t="n">
-        <v>17084</v>
+        <v>15211</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2978</v>
+        <v>4231</v>
       </c>
       <c r="C4" t="n">
-        <v>6135</v>
+        <v>5860</v>
       </c>
       <c r="D4" t="n">
-        <v>15425</v>
+        <v>13174</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1246</v>
+        <v>1841</v>
       </c>
       <c r="C5" t="n">
-        <v>8332</v>
+        <v>8796</v>
       </c>
       <c r="D5" t="n">
-        <v>7623</v>
+        <v>6749</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>401</v>
+        <v>647</v>
       </c>
       <c r="C6" t="n">
-        <v>6478</v>
+        <v>5973</v>
       </c>
       <c r="D6" t="n">
-        <v>2423</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>3040</v>
+        <v>2395</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1108</v>
+        <v>910</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5576</v>
+        <v>7869</v>
       </c>
       <c r="C2" t="n">
-        <v>9093</v>
+        <v>3620</v>
       </c>
       <c r="D2" t="n">
-        <v>27108</v>
+        <v>19972</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1978</v>
+        <v>3667</v>
       </c>
       <c r="C3" t="n">
-        <v>2432</v>
+        <v>2015</v>
       </c>
       <c r="D3" t="n">
-        <v>3737</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4351</v>
+        <v>5630</v>
       </c>
       <c r="C2" t="n">
-        <v>5724</v>
+        <v>4426</v>
       </c>
       <c r="D2" t="n">
-        <v>33294</v>
+        <v>20073</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3100</v>
+        <v>4741</v>
       </c>
       <c r="C3" t="n">
-        <v>5347</v>
+        <v>2520</v>
       </c>
       <c r="D3" t="n">
-        <v>7388</v>
+        <v>5487</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>893</v>
+        <v>1627</v>
       </c>
       <c r="C4" t="n">
-        <v>1470</v>
+        <v>1226</v>
       </c>
       <c r="D4" t="n">
-        <v>1934</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4001</v>
+        <v>5226</v>
       </c>
       <c r="C2" t="n">
-        <v>7813</v>
+        <v>3869</v>
       </c>
       <c r="D2" t="n">
-        <v>41366</v>
+        <v>15347</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3052</v>
+        <v>4267</v>
       </c>
       <c r="C3" t="n">
-        <v>4811</v>
+        <v>3080</v>
       </c>
       <c r="D3" t="n">
-        <v>11001</v>
+        <v>7425</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1697</v>
+        <v>2700</v>
       </c>
       <c r="C4" t="n">
-        <v>3584</v>
+        <v>1933</v>
       </c>
       <c r="D4" t="n">
-        <v>2922</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>419</v>
+        <v>727</v>
       </c>
       <c r="C5" t="n">
-        <v>901</v>
+        <v>765</v>
       </c>
       <c r="D5" t="n">
-        <v>1284</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4822</v>
+        <v>5815</v>
       </c>
       <c r="C2" t="n">
-        <v>11706</v>
+        <v>4521</v>
       </c>
       <c r="D2" t="n">
-        <v>38816</v>
+        <v>21134</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2876</v>
+        <v>3891</v>
       </c>
       <c r="C3" t="n">
-        <v>5516</v>
+        <v>3035</v>
       </c>
       <c r="D3" t="n">
-        <v>14842</v>
+        <v>8106</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1991</v>
+        <v>2950</v>
       </c>
       <c r="C4" t="n">
-        <v>4122</v>
+        <v>2520</v>
       </c>
       <c r="D4" t="n">
-        <v>4306</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>871</v>
+        <v>1434</v>
       </c>
       <c r="C5" t="n">
-        <v>2273</v>
+        <v>1365</v>
       </c>
       <c r="D5" t="n">
-        <v>1515</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>372</v>
       </c>
       <c r="C6" t="n">
-        <v>599</v>
+        <v>533</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6310</v>
+        <v>6541</v>
       </c>
       <c r="C2" t="n">
-        <v>8154</v>
+        <v>8632</v>
       </c>
       <c r="D2" t="n">
-        <v>31581</v>
+        <v>28083</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2756</v>
+        <v>3528</v>
       </c>
       <c r="C3" t="n">
-        <v>7064</v>
+        <v>3118</v>
       </c>
       <c r="D3" t="n">
-        <v>16409</v>
+        <v>8952</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1492</v>
+        <v>2138</v>
       </c>
       <c r="C4" t="n">
-        <v>3989</v>
+        <v>2303</v>
       </c>
       <c r="D4" t="n">
-        <v>5322</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>738</v>
+        <v>1148</v>
       </c>
       <c r="C5" t="n">
-        <v>2330</v>
+        <v>1435</v>
       </c>
       <c r="D5" t="n">
-        <v>1568</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>263</v>
+        <v>429</v>
       </c>
       <c r="C6" t="n">
-        <v>960</v>
+        <v>647</v>
       </c>
       <c r="D6" t="n">
-        <v>802</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="D7" t="n">
         <v>518</v>
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4948</v>
+        <v>5613</v>
       </c>
       <c r="C2" t="n">
-        <v>5255</v>
+        <v>7380</v>
       </c>
       <c r="D2" t="n">
-        <v>29135</v>
+        <v>30548</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3752</v>
+        <v>4208</v>
       </c>
       <c r="C3" t="n">
-        <v>6621</v>
+        <v>5536</v>
       </c>
       <c r="D3" t="n">
-        <v>17750</v>
+        <v>11645</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1856</v>
+        <v>2497</v>
       </c>
       <c r="C4" t="n">
-        <v>5736</v>
+        <v>2763</v>
       </c>
       <c r="D4" t="n">
-        <v>7395</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>990</v>
+        <v>1477</v>
       </c>
       <c r="C5" t="n">
-        <v>3237</v>
+        <v>1930</v>
       </c>
       <c r="D5" t="n">
-        <v>2226</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>456</v>
+        <v>732</v>
       </c>
       <c r="C6" t="n">
-        <v>1711</v>
+        <v>1100</v>
       </c>
       <c r="D6" t="n">
-        <v>937</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>249</v>
       </c>
       <c r="C7" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3942</v>
+        <v>5024</v>
       </c>
       <c r="C2" t="n">
-        <v>5192</v>
+        <v>3556</v>
       </c>
       <c r="D2" t="n">
-        <v>25222</v>
+        <v>33671</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3562</v>
+        <v>4037</v>
       </c>
       <c r="C3" t="n">
-        <v>5129</v>
+        <v>5668</v>
       </c>
       <c r="D3" t="n">
-        <v>18230</v>
+        <v>13831</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2388</v>
+        <v>2877</v>
       </c>
       <c r="C4" t="n">
-        <v>6045</v>
+        <v>4276</v>
       </c>
       <c r="D4" t="n">
-        <v>8987</v>
+        <v>5714</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1230</v>
+        <v>1765</v>
       </c>
       <c r="C5" t="n">
-        <v>4513</v>
+        <v>2361</v>
       </c>
       <c r="D5" t="n">
-        <v>3101</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>651</v>
+        <v>1006</v>
       </c>
       <c r="C6" t="n">
-        <v>2482</v>
+        <v>1541</v>
       </c>
       <c r="D6" t="n">
-        <v>1137</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>439</v>
       </c>
       <c r="C7" t="n">
-        <v>1187</v>
+        <v>819</v>
       </c>
       <c r="D7" t="n">
-        <v>624</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>459</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>293</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_100_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6977</v>
+        <v>1176</v>
       </c>
       <c r="C2" t="n">
-        <v>5881</v>
+        <v>4916</v>
       </c>
       <c r="D2" t="n">
-        <v>26040</v>
+        <v>16913</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3711</v>
+        <v>2100</v>
       </c>
       <c r="C3" t="n">
-        <v>3987</v>
+        <v>9680</v>
       </c>
       <c r="D3" t="n">
-        <v>15872</v>
+        <v>17332</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2964</v>
+        <v>1344</v>
       </c>
       <c r="C4" t="n">
-        <v>4935</v>
+        <v>9272</v>
       </c>
       <c r="D4" t="n">
-        <v>7020</v>
+        <v>7430</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2016</v>
+        <v>627</v>
       </c>
       <c r="C5" t="n">
-        <v>3281</v>
+        <v>6691</v>
       </c>
       <c r="D5" t="n">
-        <v>2743</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1256</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>1941</v>
+        <v>3325</v>
       </c>
       <c r="D6" t="n">
-        <v>1219</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>629</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1179</v>
+        <v>1124</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>246</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>585</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7964</v>
+        <v>1317</v>
       </c>
       <c r="C2" t="n">
-        <v>12406</v>
+        <v>7076</v>
       </c>
       <c r="D2" t="n">
-        <v>30265</v>
+        <v>20243</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4202</v>
+        <v>1433</v>
       </c>
       <c r="C3" t="n">
-        <v>4283</v>
+        <v>6491</v>
       </c>
       <c r="D3" t="n">
-        <v>16244</v>
+        <v>16079</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2824</v>
+        <v>1456</v>
       </c>
       <c r="C4" t="n">
-        <v>4359</v>
+        <v>9286</v>
       </c>
       <c r="D4" t="n">
-        <v>8336</v>
+        <v>8915</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2159</v>
+        <v>823</v>
       </c>
       <c r="C5" t="n">
-        <v>3975</v>
+        <v>7879</v>
       </c>
       <c r="D5" t="n">
-        <v>3331</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1471</v>
+        <v>372</v>
       </c>
       <c r="C6" t="n">
-        <v>2551</v>
+        <v>4842</v>
       </c>
       <c r="D6" t="n">
-        <v>1451</v>
+        <v>922</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>812</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>1517</v>
+        <v>2126</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>366</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>852</v>
+        <v>701</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>419</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9970</v>
+        <v>729</v>
       </c>
       <c r="C2" t="n">
-        <v>10117</v>
+        <v>3222</v>
       </c>
       <c r="D2" t="n">
-        <v>38740</v>
+        <v>13953</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4696</v>
+        <v>1364</v>
       </c>
       <c r="C3" t="n">
-        <v>6901</v>
+        <v>6478</v>
       </c>
       <c r="D3" t="n">
-        <v>16973</v>
+        <v>16159</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2923</v>
+        <v>1568</v>
       </c>
       <c r="C4" t="n">
-        <v>4233</v>
+        <v>9018</v>
       </c>
       <c r="D4" t="n">
-        <v>9217</v>
+        <v>9759</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2171</v>
+        <v>805</v>
       </c>
       <c r="C5" t="n">
-        <v>4023</v>
+        <v>9363</v>
       </c>
       <c r="D5" t="n">
-        <v>3998</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1608</v>
+        <v>287</v>
       </c>
       <c r="C6" t="n">
-        <v>3142</v>
+        <v>5730</v>
       </c>
       <c r="D6" t="n">
-        <v>1688</v>
+        <v>932</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>977</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>1937</v>
+        <v>1904</v>
       </c>
       <c r="D7" t="n">
-        <v>845</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>489</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1117</v>
+        <v>525</v>
       </c>
       <c r="D8" t="n">
-        <v>494</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>193</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>592</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>337</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8949</v>
+        <v>929</v>
       </c>
       <c r="C2" t="n">
-        <v>6717</v>
+        <v>4428</v>
       </c>
       <c r="D2" t="n">
-        <v>31333</v>
+        <v>13632</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5531</v>
+        <v>942</v>
       </c>
       <c r="C3" t="n">
-        <v>9626</v>
+        <v>4387</v>
       </c>
       <c r="D3" t="n">
-        <v>18695</v>
+        <v>14773</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2006</v>
+        <v>1306</v>
       </c>
       <c r="C4" t="n">
-        <v>6300</v>
+        <v>7673</v>
       </c>
       <c r="D4" t="n">
-        <v>8830</v>
+        <v>10506</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>992</v>
       </c>
       <c r="C5" t="n">
-        <v>3079</v>
+        <v>9099</v>
       </c>
       <c r="D5" t="n">
-        <v>2767</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>902</v>
+        <v>436</v>
       </c>
       <c r="C6" t="n">
-        <v>1898</v>
+        <v>7357</v>
       </c>
       <c r="D6" t="n">
-        <v>828</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>451</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>1094</v>
+        <v>3459</v>
       </c>
       <c r="D7" t="n">
-        <v>484</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>580</v>
+        <v>1053</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
+        <v>77</v>
+      </c>
+      <c r="D13" t="n">
         <v>89</v>
-      </c>
-      <c r="D13" t="n">
-        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5341</v>
+        <v>563</v>
       </c>
       <c r="C2" t="n">
-        <v>2976</v>
+        <v>2578</v>
       </c>
       <c r="D2" t="n">
-        <v>21613</v>
+        <v>10458</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6022</v>
+        <v>821</v>
       </c>
       <c r="C3" t="n">
-        <v>7468</v>
+        <v>3987</v>
       </c>
       <c r="D3" t="n">
-        <v>19587</v>
+        <v>13832</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2961</v>
+        <v>1094</v>
       </c>
       <c r="C4" t="n">
-        <v>8007</v>
+        <v>6346</v>
       </c>
       <c r="D4" t="n">
-        <v>10246</v>
+        <v>10860</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1610</v>
+        <v>1055</v>
       </c>
       <c r="C5" t="n">
-        <v>4523</v>
+        <v>8725</v>
       </c>
       <c r="D5" t="n">
-        <v>3492</v>
+        <v>4792</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1080</v>
+        <v>535</v>
       </c>
       <c r="C6" t="n">
-        <v>2414</v>
+        <v>8217</v>
       </c>
       <c r="D6" t="n">
-        <v>1028</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>429</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>1418</v>
+        <v>4688</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>750</v>
+        <v>1569</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>359</v>
+        <v>402</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>100</v>
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6618</v>
+        <v>629</v>
       </c>
       <c r="C2" t="n">
-        <v>4447</v>
+        <v>10013</v>
       </c>
       <c r="D2" t="n">
-        <v>18365</v>
+        <v>13065</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4804</v>
+        <v>611</v>
       </c>
       <c r="C3" t="n">
-        <v>4631</v>
+        <v>3015</v>
       </c>
       <c r="D3" t="n">
-        <v>18531</v>
+        <v>12625</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3719</v>
+        <v>864</v>
       </c>
       <c r="C4" t="n">
-        <v>7566</v>
+        <v>5172</v>
       </c>
       <c r="D4" t="n">
-        <v>11548</v>
+        <v>10853</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1946</v>
+        <v>989</v>
       </c>
       <c r="C5" t="n">
-        <v>6178</v>
+        <v>7622</v>
       </c>
       <c r="D5" t="n">
-        <v>4488</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1209</v>
+        <v>662</v>
       </c>
       <c r="C6" t="n">
-        <v>3361</v>
+        <v>8346</v>
       </c>
       <c r="D6" t="n">
-        <v>1392</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>616</v>
+        <v>227</v>
       </c>
       <c r="C7" t="n">
-        <v>1880</v>
+        <v>6034</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>218</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1038</v>
+        <v>2714</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>519</v>
+        <v>794</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
         <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
+        <v>64</v>
+      </c>
+      <c r="D14" t="n">
         <v>54</v>
-      </c>
-      <c r="D14" t="n">
-        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3882</v>
+        <v>442</v>
       </c>
       <c r="C2" t="n">
-        <v>2008</v>
+        <v>5607</v>
       </c>
       <c r="D2" t="n">
-        <v>12660</v>
+        <v>9615</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5067</v>
+        <v>853</v>
       </c>
       <c r="C3" t="n">
-        <v>4410</v>
+        <v>4950</v>
       </c>
       <c r="D3" t="n">
-        <v>18067</v>
+        <v>13685</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4124</v>
+        <v>1341</v>
       </c>
       <c r="C4" t="n">
-        <v>7120</v>
+        <v>7580</v>
       </c>
       <c r="D4" t="n">
-        <v>12421</v>
+        <v>10961</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2070</v>
+        <v>648</v>
       </c>
       <c r="C5" t="n">
-        <v>7390</v>
+        <v>11510</v>
       </c>
       <c r="D5" t="n">
-        <v>4888</v>
+        <v>4972</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1071</v>
+        <v>209</v>
       </c>
       <c r="C6" t="n">
-        <v>4148</v>
+        <v>7630</v>
       </c>
       <c r="D6" t="n">
-        <v>1367</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>1952</v>
+        <v>2659</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>844</v>
+        <v>778</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
         <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D13" t="n">
         <v>52</v>
-      </c>
-      <c r="D13" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4440</v>
+        <v>312</v>
       </c>
       <c r="C2" t="n">
-        <v>5196</v>
+        <v>3190</v>
       </c>
       <c r="D2" t="n">
-        <v>13479</v>
+        <v>7429</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3894</v>
+        <v>585</v>
       </c>
       <c r="C3" t="n">
-        <v>2909</v>
+        <v>4648</v>
       </c>
       <c r="D3" t="n">
-        <v>16117</v>
+        <v>12170</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3940</v>
+        <v>935</v>
       </c>
       <c r="C4" t="n">
-        <v>5713</v>
+        <v>5928</v>
       </c>
       <c r="D4" t="n">
-        <v>12964</v>
+        <v>10609</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2581</v>
+        <v>641</v>
       </c>
       <c r="C5" t="n">
-        <v>7182</v>
+        <v>8661</v>
       </c>
       <c r="D5" t="n">
-        <v>5896</v>
+        <v>5201</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1343</v>
+        <v>208</v>
       </c>
       <c r="C6" t="n">
-        <v>5550</v>
+        <v>7507</v>
       </c>
       <c r="D6" t="n">
-        <v>1869</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>47</v>
       </c>
       <c r="C7" t="n">
-        <v>2893</v>
+        <v>3352</v>
       </c>
       <c r="D7" t="n">
-        <v>689</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1272</v>
+        <v>904</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>466</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3383</v>
+        <v>488</v>
       </c>
       <c r="C2" t="n">
-        <v>2942</v>
+        <v>4981</v>
       </c>
       <c r="D2" t="n">
-        <v>9887</v>
+        <v>9455</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3567</v>
+        <v>386</v>
       </c>
       <c r="C3" t="n">
-        <v>3476</v>
+        <v>3411</v>
       </c>
       <c r="D3" t="n">
-        <v>14923</v>
+        <v>10709</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3579</v>
+        <v>686</v>
       </c>
       <c r="C4" t="n">
-        <v>4574</v>
+        <v>5185</v>
       </c>
       <c r="D4" t="n">
-        <v>13118</v>
+        <v>10454</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2856</v>
+        <v>689</v>
       </c>
       <c r="C5" t="n">
-        <v>6758</v>
+        <v>7116</v>
       </c>
       <c r="D5" t="n">
-        <v>6644</v>
+        <v>5977</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1577</v>
+        <v>357</v>
       </c>
       <c r="C6" t="n">
-        <v>6300</v>
+        <v>7982</v>
       </c>
       <c r="D6" t="n">
-        <v>2231</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>3767</v>
+        <v>5338</v>
       </c>
       <c r="D7" t="n">
-        <v>779</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>1667</v>
+        <v>1992</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>562</v>
+        <v>524</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>167</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5726</v>
+        <v>481</v>
       </c>
       <c r="C2" t="n">
-        <v>5045</v>
+        <v>7862</v>
       </c>
       <c r="D2" t="n">
-        <v>22560</v>
+        <v>13167</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2943</v>
+        <v>354</v>
       </c>
       <c r="C3" t="n">
-        <v>2884</v>
+        <v>3629</v>
       </c>
       <c r="D3" t="n">
-        <v>13442</v>
+        <v>9818</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3106</v>
+        <v>491</v>
       </c>
       <c r="C4" t="n">
-        <v>3993</v>
+        <v>4225</v>
       </c>
       <c r="D4" t="n">
-        <v>12853</v>
+        <v>10177</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2861</v>
+        <v>622</v>
       </c>
       <c r="C5" t="n">
-        <v>5694</v>
+        <v>6078</v>
       </c>
       <c r="D5" t="n">
-        <v>7374</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1879</v>
+        <v>453</v>
       </c>
       <c r="C6" t="n">
-        <v>6490</v>
+        <v>7522</v>
       </c>
       <c r="D6" t="n">
-        <v>2795</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>701</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>4733</v>
+        <v>6423</v>
       </c>
       <c r="D7" t="n">
-        <v>956</v>
+        <v>933</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>2444</v>
+        <v>3401</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>929</v>
+        <v>1113</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>193</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8636</v>
+        <v>5502</v>
       </c>
       <c r="C2" t="n">
-        <v>3999</v>
+        <v>26210</v>
       </c>
       <c r="D2" t="n">
-        <v>12932</v>
+        <v>11894</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4052</v>
+        <v>308</v>
       </c>
       <c r="C2" t="n">
-        <v>2825</v>
+        <v>11323</v>
       </c>
       <c r="D2" t="n">
-        <v>16604</v>
+        <v>10735</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4009</v>
+        <v>332</v>
       </c>
       <c r="C3" t="n">
-        <v>3647</v>
+        <v>4746</v>
       </c>
       <c r="D3" t="n">
-        <v>15211</v>
+        <v>9591</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4231</v>
+        <v>379</v>
       </c>
       <c r="C4" t="n">
-        <v>5860</v>
+        <v>3879</v>
       </c>
       <c r="D4" t="n">
-        <v>13174</v>
+        <v>9718</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1841</v>
+        <v>529</v>
       </c>
       <c r="C5" t="n">
-        <v>8796</v>
+        <v>5128</v>
       </c>
       <c r="D5" t="n">
-        <v>6749</v>
+        <v>6769</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>647</v>
+        <v>475</v>
       </c>
       <c r="C6" t="n">
-        <v>5973</v>
+        <v>6873</v>
       </c>
       <c r="D6" t="n">
-        <v>2184</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>2395</v>
+        <v>6788</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>910</v>
+        <v>4554</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>1931</v>
       </c>
       <c r="D9" t="n">
-        <v>189</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>588</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7869</v>
+        <v>4184</v>
       </c>
       <c r="C2" t="n">
-        <v>3620</v>
+        <v>13171</v>
       </c>
       <c r="D2" t="n">
-        <v>19972</v>
+        <v>23451</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3667</v>
+        <v>1774</v>
       </c>
       <c r="C3" t="n">
-        <v>2015</v>
+        <v>10350</v>
       </c>
       <c r="D3" t="n">
-        <v>2811</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5630</v>
+        <v>2347</v>
       </c>
       <c r="C2" t="n">
-        <v>4426</v>
+        <v>5501</v>
       </c>
       <c r="D2" t="n">
-        <v>20073</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4741</v>
+        <v>2484</v>
       </c>
       <c r="C3" t="n">
-        <v>2520</v>
+        <v>10320</v>
       </c>
       <c r="D3" t="n">
-        <v>5487</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1627</v>
+        <v>831</v>
       </c>
       <c r="C4" t="n">
-        <v>1226</v>
+        <v>6407</v>
       </c>
       <c r="D4" t="n">
-        <v>1747</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5226</v>
+        <v>3255</v>
       </c>
       <c r="C2" t="n">
-        <v>3869</v>
+        <v>4575</v>
       </c>
       <c r="D2" t="n">
-        <v>15347</v>
+        <v>33672</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4267</v>
+        <v>1996</v>
       </c>
       <c r="C3" t="n">
-        <v>3080</v>
+        <v>6603</v>
       </c>
       <c r="D3" t="n">
-        <v>7425</v>
+        <v>9864</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2700</v>
+        <v>1426</v>
       </c>
       <c r="C4" t="n">
-        <v>1933</v>
+        <v>8527</v>
       </c>
       <c r="D4" t="n">
-        <v>2411</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>727</v>
+        <v>388</v>
       </c>
       <c r="C5" t="n">
-        <v>765</v>
+        <v>3655</v>
       </c>
       <c r="D5" t="n">
-        <v>1250</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>797</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5815</v>
+        <v>2663</v>
       </c>
       <c r="C2" t="n">
-        <v>4521</v>
+        <v>5266</v>
       </c>
       <c r="D2" t="n">
-        <v>21134</v>
+        <v>33623</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3891</v>
+        <v>2125</v>
       </c>
       <c r="C3" t="n">
-        <v>3035</v>
+        <v>4838</v>
       </c>
       <c r="D3" t="n">
-        <v>8106</v>
+        <v>12788</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2950</v>
+        <v>1467</v>
       </c>
       <c r="C4" t="n">
-        <v>2520</v>
+        <v>7233</v>
       </c>
       <c r="D4" t="n">
-        <v>3229</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1434</v>
+        <v>747</v>
       </c>
       <c r="C5" t="n">
-        <v>1365</v>
+        <v>6151</v>
       </c>
       <c r="D5" t="n">
-        <v>1423</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>372</v>
+        <v>217</v>
       </c>
       <c r="C6" t="n">
-        <v>533</v>
+        <v>1987</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6541</v>
+        <v>2390</v>
       </c>
       <c r="C2" t="n">
-        <v>8632</v>
+        <v>7677</v>
       </c>
       <c r="D2" t="n">
-        <v>28083</v>
+        <v>30148</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3528</v>
+        <v>1951</v>
       </c>
       <c r="C3" t="n">
-        <v>3118</v>
+        <v>4415</v>
       </c>
       <c r="D3" t="n">
-        <v>8952</v>
+        <v>14908</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2138</v>
+        <v>1521</v>
       </c>
       <c r="C4" t="n">
-        <v>2303</v>
+        <v>5863</v>
       </c>
       <c r="D4" t="n">
-        <v>3479</v>
+        <v>5079</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1148</v>
+        <v>932</v>
       </c>
       <c r="C5" t="n">
-        <v>1435</v>
+        <v>6552</v>
       </c>
       <c r="D5" t="n">
-        <v>1385</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="C6" t="n">
-        <v>647</v>
+        <v>3925</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>282</v>
+        <v>1072</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5613</v>
+        <v>2494</v>
       </c>
       <c r="C2" t="n">
-        <v>7380</v>
+        <v>18398</v>
       </c>
       <c r="D2" t="n">
-        <v>30548</v>
+        <v>30722</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4208</v>
+        <v>1764</v>
       </c>
       <c r="C3" t="n">
-        <v>5536</v>
+        <v>5170</v>
       </c>
       <c r="D3" t="n">
-        <v>11645</v>
+        <v>15978</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2497</v>
+        <v>1472</v>
       </c>
       <c r="C4" t="n">
-        <v>2763</v>
+        <v>5059</v>
       </c>
       <c r="D4" t="n">
-        <v>4529</v>
+        <v>6528</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1477</v>
+        <v>1039</v>
       </c>
       <c r="C5" t="n">
-        <v>1930</v>
+        <v>6041</v>
       </c>
       <c r="D5" t="n">
-        <v>1751</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>732</v>
+        <v>566</v>
       </c>
       <c r="C6" t="n">
-        <v>1100</v>
+        <v>5047</v>
       </c>
       <c r="D6" t="n">
-        <v>889</v>
+        <v>986</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="C7" t="n">
-        <v>492</v>
+        <v>2301</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>254</v>
+        <v>615</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5024</v>
+        <v>2340</v>
       </c>
       <c r="C2" t="n">
-        <v>3556</v>
+        <v>12069</v>
       </c>
       <c r="D2" t="n">
-        <v>33671</v>
+        <v>24791</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4037</v>
+        <v>2411</v>
       </c>
       <c r="C3" t="n">
-        <v>5668</v>
+        <v>9506</v>
       </c>
       <c r="D3" t="n">
-        <v>13831</v>
+        <v>17067</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2877</v>
+        <v>960</v>
       </c>
       <c r="C4" t="n">
-        <v>4276</v>
+        <v>8761</v>
       </c>
       <c r="D4" t="n">
-        <v>5714</v>
+        <v>5758</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1765</v>
+        <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>2361</v>
+        <v>4946</v>
       </c>
       <c r="D5" t="n">
-        <v>2231</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1006</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>1541</v>
+        <v>2254</v>
       </c>
       <c r="D6" t="n">
-        <v>1025</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>439</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>819</v>
+        <v>602</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
